--- a/survey_templates/035_search_relevance_evaluation_survey--survey_templates.xlsx
+++ b/survey_templates/035_search_relevance_evaluation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>search_relevance_evaluation_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>search_relevance_results</t>
+          <t>search_results</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Search Relevance Results</t>
+          <t>What were the search results?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>search_relevance_results_clarity</t>
+          <t>search_results_clarity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Result clarity</t>
+          <t>How clear were the search results?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>search_relevance_results_satisfaction</t>
+          <t>search_results_satisfaction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Result Satisfaction</t>
+          <t>How satisfied were you with the search results?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>search_results_clarity</t>
+          <t>relevance_results_important</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Search Results Clarity</t>
+          <t>How important is it to you that the search results are relevant?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>search_result_clarity_important</t>
+          <t>result_clarity_important</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Result clarity important</t>
+          <t>How important is it to you that the search results are clear?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>search_result_satisfaction_important</t>
+          <t>relevant_results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Result Satisfaction Important</t>
+          <t>What are the relevant search results?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>search_relevance_results_relevant</t>
+          <t>result_satisfaction_important</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Relevance Results</t>
+          <t>How important is it to you that the search results are satisfying?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>search_result_relevant_important</t>
+          <t>search_results_clarity_scale</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Relevance Results Important</t>
+          <t>How clear are the search results?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>search_results_satisfaction_important</t>
+          <t>search_results_satisfaction_scale</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Result Satisfaction Important</t>
+          <t>How satisfied are you with the search results?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>result_clarity_important</t>
+          <t>open_ended</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Result Clarity Important</t>
+          <t>What did you think about the search results?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>result_satisfaction_important</t>
+          <t>search_results_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Result Satisfaction Important</t>
+          <t>How clear are the search results on a scale of 1-10?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>search_relevance_results_clarity_important</t>
+          <t>search_results_10_10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Relevance Results Clarity Important</t>
+          <t>How satisfied are you with the search results on a scale of 1-10?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>search_relevance_results_satisfaction_important</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Relevance Results Satisfaction Important</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>search_results_clarity_scale_10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Search Results Clarity</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>search_results_clarity_score_10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Clarity Results</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_scale_10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Satisfaction Results</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_score_10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Satisfaction Results</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>search_results_clarity_10_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Clarity Results 10</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_10_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Satisfaction Results 10</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>open_ended_10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Open-Ended</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>search_results_10_10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Search Results 10</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>search_results_10_20</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Search Results 20</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>search_results_10_30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Search Results 30</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>search_results_10_40</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Search Results 40</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,75 +850,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>search_result_clarity_important_choices</t>
+          <t>search_results_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>very_important</t>
+          <t>relevant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Very Important</t>
+          <t>Relevant</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>search_result_clarity_important_choices</t>
+          <t>search_results_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>somewhat_important</t>
+          <t>somewhat_relevant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Somewhat Important</t>
+          <t>Somewhat Relevant</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>search_result_clarity_important_choices</t>
+          <t>search_results_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_very_important</t>
+          <t>not_very_relevant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Not Very Important</t>
+          <t>Not Very Relevant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>search_result_clarity_important_choices</t>
+          <t>search_results_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_at_all_important</t>
+          <t>not_at_all_relevant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not at All Important</t>
+          <t>Not at All Relevant</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>search_result_satisfaction_important_choices</t>
+          <t>relevance_results_important_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +935,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>search_result_satisfaction_important_choices</t>
+          <t>relevance_results_important_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +952,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>search_result_satisfaction_important_choices</t>
+          <t>relevance_results_important_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>search_result_satisfaction_important_choices</t>
+          <t>relevance_results_important_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,75 +986,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>search_relevance_results_relevant_choices</t>
+          <t>result_clarity_important_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>relevant</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Relevant</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>search_relevance_results_relevant_choices</t>
+          <t>result_clarity_important_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>somewhat_relevant</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Somewhat Relevant</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>search_relevance_results_relevant_choices</t>
+          <t>result_clarity_important_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_relevant</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Not Relevant</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>search_relevance_results_relevant_choices</t>
+          <t>result_clarity_important_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_at_all_relevant</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not at All Relevant</t>
+          <t>Not at All Important</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>search_result_relevant_important_choices</t>
+          <t>result_satisfaction_important_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1071,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>search_result_relevant_important_choices</t>
+          <t>result_satisfaction_important_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1088,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>search_result_relevant_important_choices</t>
+          <t>result_satisfaction_important_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1105,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>search_result_relevant_important_choices</t>
+          <t>result_satisfaction_important_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1390,346 +1114,6 @@
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>Not at All Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Somewhat Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Not Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>search_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>not_at_all_important</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Not at All Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>result_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>result_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Somewhat Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>result_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Not Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>result_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>not_at_all_important</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Not at All Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>result_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>result_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Somewhat Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>result_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>result_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>not_at_all_important</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Not at All Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>search_relevance_results_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>search_relevance_results_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Somewhat Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>search_relevance_results_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Not Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>search_relevance_results_clarity_important_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>not_at_all_important</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Not at All Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>search_relevance_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>very_important</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>search_relevance_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>somewhat_important</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Somewhat Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>search_relevance_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>not_very_important</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Not Very Important</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>search_relevance_results_satisfaction_important_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>not_at_all_important</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>Not at All Important</t>
         </is>
